--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.01_Q100_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005492960313728188</v>
+        <v>0.0002536883590057705</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005492960313728188</v>
+        <v>0.0002536883590057705</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002291180432831546</v>
+        <v>0.0001431810416383691</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00147755845037216</v>
+        <v>0.0007013064232469246</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00147755845037216</v>
+        <v>0.0007013064232469246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006128121691021795</v>
+        <v>0.0003750514879713531</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.003038220036449645</v>
+        <v>0.001434423115595629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003038220036449645</v>
+        <v>0.001434423115595629</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001163181765179744</v>
+        <v>0.0006974083218169517</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.004046544952527928</v>
+        <v>0.001913415428356578</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004046544952527928</v>
+        <v>0.001913415428356578</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001505996163574809</v>
+        <v>0.0009304409299845431</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003868243514147529</v>
+        <v>0.001825583800936903</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003868243514147529</v>
+        <v>0.001825583800936903</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001428725476426005</v>
+        <v>0.0008880435163970648</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.003435921408468191</v>
+        <v>0.001623569316507299</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003435921408468191</v>
+        <v>0.001623569316507299</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001276845829422837</v>
+        <v>0.000792278705816296</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.003051253526207992</v>
+        <v>0.001443871737393933</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003051253526207992</v>
+        <v>0.001443871737393933</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001151326934528576</v>
+        <v>0.0007146894039476036</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.002796923172141762</v>
+        <v>0.001324790925803283</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002796923172141762</v>
+        <v>0.001324790925803283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001096211400928261</v>
+        <v>0.00066338191189838</v>
       </c>
     </row>
   </sheetData>
